--- a/artfynd/A 12576-2023 artfynd.xlsx
+++ b/artfynd/A 12576-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12576-2023 artfynd.xlsx
+++ b/artfynd/A 12576-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13831345</v>
+        <v>13831337</v>
       </c>
       <c r="B2" t="n">
-        <v>60372</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101800</v>
+        <v>101258</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lamellsnäcka</t>
+          <t>Bukspolsnäcka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spermodea lamellata</t>
+          <t>Macrogastra ventricosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Jeffreys, 1830)</t>
+          <t>(Draparnaud, 1801)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433886.2042924084</v>
+        <v>433886</v>
       </c>
       <c r="R2" t="n">
-        <v>6197475.006818997</v>
+        <v>6197475</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -753,19 +748,9 @@
           <t>1981-07-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1981-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -819,16 +804,11 @@
         <v>13831341</v>
       </c>
       <c r="B3" t="n">
-        <v>60229</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -861,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433886.2042924084</v>
+        <v>433886</v>
       </c>
       <c r="R3" t="n">
-        <v>6197475.006818997</v>
+        <v>6197475</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -894,19 +874,9 @@
           <t>1981-07-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1981-07-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -957,37 +927,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>13831337</v>
+        <v>13831345</v>
       </c>
       <c r="B4" t="n">
-        <v>60165</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101258</v>
+        <v>101800</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bukspolsnäcka</t>
+          <t>Lamellsnäcka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Macrogastra ventricosa</t>
+          <t>Spermodea lamellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Draparnaud, 1801)</t>
+          <t>(Jeffreys, 1830)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1002,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433886.2042924084</v>
+        <v>433886</v>
       </c>
       <c r="R4" t="n">
-        <v>6197475.006818997</v>
+        <v>6197475</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1035,19 +1000,9 @@
           <t>1981-07-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1981-07-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 12576-2023 artfynd.xlsx
+++ b/artfynd/A 12576-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
           <t>Markfaunaregistret GNM</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13831337</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
           <t>Markfaunaregistret GNM</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13831341</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,8 +1065,18 @@
           <t>Markfaunaregistret GNM</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13831345</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>